--- a/output/2024_estado_nutricional_por_comuna.xlsx
+++ b/output/2024_estado_nutricional_por_comuna.xlsx
@@ -448,16 +448,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -473,7 +465,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -481,30 +473,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -803,276 +777,276 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:89">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" t="s">
         <v>55</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" t="s">
         <v>56</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" t="s">
         <v>58</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" t="s">
         <v>59</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" t="s">
         <v>61</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" t="s">
         <v>62</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" t="s">
         <v>63</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" t="s">
         <v>64</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BO1" t="s">
         <v>65</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" t="s">
         <v>66</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" t="s">
         <v>67</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BR1" t="s">
         <v>68</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BS1" t="s">
         <v>69</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BT1" t="s">
         <v>70</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BU1" t="s">
         <v>71</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BV1" t="s">
         <v>72</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BW1" t="s">
         <v>73</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BX1" t="s">
         <v>74</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BY1" t="s">
         <v>75</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="BZ1" t="s">
         <v>76</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CA1" t="s">
         <v>77</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CB1" t="s">
         <v>78</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CC1" t="s">
         <v>79</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CD1" t="s">
         <v>80</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CE1" t="s">
         <v>81</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CF1" t="s">
         <v>82</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CG1" t="s">
         <v>83</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CH1" t="s">
         <v>84</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CI1" t="s">
         <v>85</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CJ1" t="s">
         <v>86</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CK1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:89">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -1284,7 +1258,7 @@
       </c>
     </row>
     <row r="3" spans="1:89">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -1508,7 +1482,7 @@
       </c>
     </row>
     <row r="4" spans="1:89">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -1732,7 +1706,7 @@
       </c>
     </row>
     <row r="5" spans="1:89">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -1956,7 +1930,7 @@
       </c>
     </row>
     <row r="6" spans="1:89">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -2207,7 +2181,7 @@
       </c>
     </row>
     <row r="7" spans="1:89">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -2458,7 +2432,7 @@
       </c>
     </row>
     <row r="8" spans="1:89">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -2709,7 +2683,7 @@
       </c>
     </row>
     <row r="9" spans="1:89">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -2927,7 +2901,7 @@
       </c>
     </row>
     <row r="10" spans="1:89">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -3178,7 +3152,7 @@
       </c>
     </row>
     <row r="11" spans="1:89">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -3405,7 +3379,7 @@
       </c>
     </row>
     <row r="12" spans="1:89">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -3650,7 +3624,7 @@
       </c>
     </row>
     <row r="13" spans="1:89">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -3901,7 +3875,7 @@
       </c>
     </row>
     <row r="14" spans="1:89">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -4152,7 +4126,7 @@
       </c>
     </row>
     <row r="15" spans="1:89">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -4370,7 +4344,7 @@
       </c>
     </row>
     <row r="16" spans="1:89">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -4621,7 +4595,7 @@
       </c>
     </row>
     <row r="17" spans="1:89">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -4872,7 +4846,7 @@
       </c>
     </row>
     <row r="18" spans="1:89">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -5117,7 +5091,7 @@
       </c>
     </row>
     <row r="19" spans="1:89">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -5356,7 +5330,7 @@
       </c>
     </row>
     <row r="20" spans="1:89">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -5601,7 +5575,7 @@
       </c>
     </row>
     <row r="21" spans="1:89">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -5846,7 +5820,7 @@
       </c>
     </row>
     <row r="22" spans="1:89">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -6097,7 +6071,7 @@
       </c>
     </row>
     <row r="23" spans="1:89">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -6342,7 +6316,7 @@
       </c>
     </row>
     <row r="24" spans="1:89">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -6593,7 +6567,7 @@
       </c>
     </row>
     <row r="25" spans="1:89">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -6844,7 +6818,7 @@
       </c>
     </row>
     <row r="26" spans="1:89">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -7095,7 +7069,7 @@
       </c>
     </row>
     <row r="27" spans="1:89">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -7340,7 +7314,7 @@
       </c>
     </row>
     <row r="28" spans="1:89">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -7558,7 +7532,7 @@
       </c>
     </row>
     <row r="29" spans="1:89">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -7809,7 +7783,7 @@
       </c>
     </row>
     <row r="30" spans="1:89">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -8054,7 +8028,7 @@
       </c>
     </row>
     <row r="31" spans="1:89">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -8299,7 +8273,7 @@
       </c>
     </row>
     <row r="32" spans="1:89">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -8532,7 +8506,7 @@
       </c>
     </row>
     <row r="33" spans="1:89">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -8771,7 +8745,7 @@
       </c>
     </row>
     <row r="34" spans="1:89">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -9022,7 +8996,7 @@
       </c>
     </row>
     <row r="35" spans="1:89">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -9261,7 +9235,7 @@
       </c>
     </row>
     <row r="36" spans="1:89">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -9506,7 +9480,7 @@
       </c>
     </row>
     <row r="37" spans="1:89">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -9751,7 +9725,7 @@
       </c>
     </row>
     <row r="38" spans="1:89">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -10002,7 +9976,7 @@
       </c>
     </row>
     <row r="39" spans="1:89">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -10235,7 +10209,7 @@
       </c>
     </row>
     <row r="40" spans="1:89">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -10474,7 +10448,7 @@
       </c>
     </row>
     <row r="41" spans="1:89">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -10725,7 +10699,7 @@
       </c>
     </row>
     <row r="42" spans="1:89">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -10976,7 +10950,7 @@
       </c>
     </row>
     <row r="43" spans="1:89">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -11221,7 +11195,7 @@
       </c>
     </row>
     <row r="44" spans="1:89">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -11472,7 +11446,7 @@
       </c>
     </row>
     <row r="45" spans="1:89">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -11684,7 +11658,7 @@
       </c>
     </row>
     <row r="46" spans="1:89">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -11935,7 +11909,7 @@
       </c>
     </row>
     <row r="47" spans="1:89">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -12147,7 +12121,7 @@
       </c>
     </row>
     <row r="48" spans="1:89">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -12398,7 +12372,7 @@
       </c>
     </row>
     <row r="49" spans="1:89">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -12649,7 +12623,7 @@
       </c>
     </row>
     <row r="50" spans="1:89">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -12867,7 +12841,7 @@
       </c>
     </row>
     <row r="51" spans="1:89">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -13106,7 +13080,7 @@
       </c>
     </row>
     <row r="52" spans="1:89">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -13315,7 +13289,7 @@
       </c>
     </row>
     <row r="53" spans="1:89">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -13570,84 +13544,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>46</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>57</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>67</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>68</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>78</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -13715,7 +13689,7 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -13783,7 +13757,7 @@
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -13851,7 +13825,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -13919,7 +13893,7 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -13996,7 +13970,7 @@
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -14073,7 +14047,7 @@
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -14150,7 +14124,7 @@
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -14218,7 +14192,7 @@
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -14295,7 +14269,7 @@
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -14366,7 +14340,7 @@
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -14443,7 +14417,7 @@
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -14520,7 +14494,7 @@
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -14597,7 +14571,7 @@
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -14665,7 +14639,7 @@
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -14742,7 +14716,7 @@
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -14819,7 +14793,7 @@
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -14896,7 +14870,7 @@
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -14967,7 +14941,7 @@
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -15044,7 +15018,7 @@
       </c>
     </row>
     <row r="21" spans="1:25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -15121,7 +15095,7 @@
       </c>
     </row>
     <row r="22" spans="1:25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -15198,7 +15172,7 @@
       </c>
     </row>
     <row r="23" spans="1:25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -15275,7 +15249,7 @@
       </c>
     </row>
     <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -15352,7 +15326,7 @@
       </c>
     </row>
     <row r="25" spans="1:25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -15429,7 +15403,7 @@
       </c>
     </row>
     <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -15506,7 +15480,7 @@
       </c>
     </row>
     <row r="27" spans="1:25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -15583,7 +15557,7 @@
       </c>
     </row>
     <row r="28" spans="1:25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -15651,7 +15625,7 @@
       </c>
     </row>
     <row r="29" spans="1:25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -15728,7 +15702,7 @@
       </c>
     </row>
     <row r="30" spans="1:25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -15805,7 +15779,7 @@
       </c>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -15882,7 +15856,7 @@
       </c>
     </row>
     <row r="32" spans="1:25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -15953,7 +15927,7 @@
       </c>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -16030,7 +16004,7 @@
       </c>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -16107,7 +16081,7 @@
       </c>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -16178,7 +16152,7 @@
       </c>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -16255,7 +16229,7 @@
       </c>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -16332,7 +16306,7 @@
       </c>
     </row>
     <row r="38" spans="1:25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -16409,7 +16383,7 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -16480,7 +16454,7 @@
       </c>
     </row>
     <row r="40" spans="1:25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -16557,7 +16531,7 @@
       </c>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -16634,7 +16608,7 @@
       </c>
     </row>
     <row r="42" spans="1:25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -16711,7 +16685,7 @@
       </c>
     </row>
     <row r="43" spans="1:25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -16788,7 +16762,7 @@
       </c>
     </row>
     <row r="44" spans="1:25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -16865,7 +16839,7 @@
       </c>
     </row>
     <row r="45" spans="1:25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -16933,7 +16907,7 @@
       </c>
     </row>
     <row r="46" spans="1:25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -17010,7 +16984,7 @@
       </c>
     </row>
     <row r="47" spans="1:25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -17078,7 +17052,7 @@
       </c>
     </row>
     <row r="48" spans="1:25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -17155,7 +17129,7 @@
       </c>
     </row>
     <row r="49" spans="1:25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -17232,7 +17206,7 @@
       </c>
     </row>
     <row r="50" spans="1:25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -17300,7 +17274,7 @@
       </c>
     </row>
     <row r="51" spans="1:25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -17377,7 +17351,7 @@
       </c>
     </row>
     <row r="52" spans="1:25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -17454,7 +17428,7 @@
       </c>
     </row>
     <row r="53" spans="1:25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -17541,84 +17515,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>47</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>69</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>70</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>80</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -17686,7 +17660,7 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -17754,7 +17728,7 @@
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -17822,7 +17796,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -17890,7 +17864,7 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -17967,7 +17941,7 @@
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -18044,7 +18018,7 @@
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -18121,7 +18095,7 @@
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -18183,7 +18157,7 @@
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -18260,7 +18234,7 @@
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -18325,7 +18299,7 @@
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -18396,7 +18370,7 @@
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -18473,7 +18447,7 @@
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -18550,7 +18524,7 @@
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -18618,7 +18592,7 @@
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -18695,7 +18669,7 @@
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -18772,7 +18746,7 @@
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -18843,7 +18817,7 @@
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -18914,7 +18888,7 @@
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -18985,7 +18959,7 @@
       </c>
     </row>
     <row r="21" spans="1:25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -19056,7 +19030,7 @@
       </c>
     </row>
     <row r="22" spans="1:25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -19133,7 +19107,7 @@
       </c>
     </row>
     <row r="23" spans="1:25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -19204,7 +19178,7 @@
       </c>
     </row>
     <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -19281,7 +19255,7 @@
       </c>
     </row>
     <row r="25" spans="1:25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -19358,7 +19332,7 @@
       </c>
     </row>
     <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -19435,7 +19409,7 @@
       </c>
     </row>
     <row r="27" spans="1:25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -19506,7 +19480,7 @@
       </c>
     </row>
     <row r="28" spans="1:25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -19574,7 +19548,7 @@
       </c>
     </row>
     <row r="29" spans="1:25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -19651,7 +19625,7 @@
       </c>
     </row>
     <row r="30" spans="1:25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -19728,7 +19702,7 @@
       </c>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -19799,7 +19773,7 @@
       </c>
     </row>
     <row r="32" spans="1:25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -19870,7 +19844,7 @@
       </c>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -19941,7 +19915,7 @@
       </c>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -20018,7 +19992,7 @@
       </c>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -20089,7 +20063,7 @@
       </c>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -20160,7 +20134,7 @@
       </c>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -20231,7 +20205,7 @@
       </c>
     </row>
     <row r="38" spans="1:25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -20308,7 +20282,7 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -20379,7 +20353,7 @@
       </c>
     </row>
     <row r="40" spans="1:25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -20450,7 +20424,7 @@
       </c>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -20527,7 +20501,7 @@
       </c>
     </row>
     <row r="42" spans="1:25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -20604,7 +20578,7 @@
       </c>
     </row>
     <row r="43" spans="1:25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -20675,7 +20649,7 @@
       </c>
     </row>
     <row r="44" spans="1:25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -20752,7 +20726,7 @@
       </c>
     </row>
     <row r="45" spans="1:25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -20814,7 +20788,7 @@
       </c>
     </row>
     <row r="46" spans="1:25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -20891,7 +20865,7 @@
       </c>
     </row>
     <row r="47" spans="1:25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -20947,7 +20921,7 @@
       </c>
     </row>
     <row r="48" spans="1:25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -21024,7 +20998,7 @@
       </c>
     </row>
     <row r="49" spans="1:25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -21101,7 +21075,7 @@
       </c>
     </row>
     <row r="50" spans="1:25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -21169,7 +21143,7 @@
       </c>
     </row>
     <row r="51" spans="1:25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -21234,7 +21208,7 @@
       </c>
     </row>
     <row r="52" spans="1:25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -21299,7 +21273,7 @@
       </c>
     </row>
     <row r="53" spans="1:25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -21380,84 +21354,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>49</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>60</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>61</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>71</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>72</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>82</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -21501,7 +21475,7 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -21557,7 +21531,7 @@
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -21613,7 +21587,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -21669,7 +21643,7 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -21728,7 +21702,7 @@
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -21787,7 +21761,7 @@
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -21846,7 +21820,7 @@
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -21902,7 +21876,7 @@
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -21961,7 +21935,7 @@
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -22014,7 +21988,7 @@
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -22073,7 +22047,7 @@
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -22132,7 +22106,7 @@
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -22191,7 +22165,7 @@
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -22241,7 +22215,7 @@
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -22300,7 +22274,7 @@
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -22359,7 +22333,7 @@
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -22418,7 +22392,7 @@
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -22477,7 +22451,7 @@
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -22536,7 +22510,7 @@
       </c>
     </row>
     <row r="21" spans="1:25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -22595,7 +22569,7 @@
       </c>
     </row>
     <row r="22" spans="1:25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -22654,7 +22628,7 @@
       </c>
     </row>
     <row r="23" spans="1:25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -22713,7 +22687,7 @@
       </c>
     </row>
     <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -22772,7 +22746,7 @@
       </c>
     </row>
     <row r="25" spans="1:25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -22831,7 +22805,7 @@
       </c>
     </row>
     <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -22890,7 +22864,7 @@
       </c>
     </row>
     <row r="27" spans="1:25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -22949,7 +22923,7 @@
       </c>
     </row>
     <row r="28" spans="1:25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -22999,7 +22973,7 @@
       </c>
     </row>
     <row r="29" spans="1:25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -23058,7 +23032,7 @@
       </c>
     </row>
     <row r="30" spans="1:25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -23111,7 +23085,7 @@
       </c>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -23170,7 +23144,7 @@
       </c>
     </row>
     <row r="32" spans="1:25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -23229,7 +23203,7 @@
       </c>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -23282,7 +23256,7 @@
       </c>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -23341,7 +23315,7 @@
       </c>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -23400,7 +23374,7 @@
       </c>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -23459,7 +23433,7 @@
       </c>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -23518,7 +23492,7 @@
       </c>
     </row>
     <row r="38" spans="1:25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -23577,7 +23551,7 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -23636,7 +23610,7 @@
       </c>
     </row>
     <row r="40" spans="1:25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -23695,7 +23669,7 @@
       </c>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -23754,7 +23728,7 @@
       </c>
     </row>
     <row r="42" spans="1:25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -23813,7 +23787,7 @@
       </c>
     </row>
     <row r="43" spans="1:25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -23872,7 +23846,7 @@
       </c>
     </row>
     <row r="44" spans="1:25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -23931,7 +23905,7 @@
       </c>
     </row>
     <row r="45" spans="1:25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -23981,7 +23955,7 @@
       </c>
     </row>
     <row r="46" spans="1:25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -24040,7 +24014,7 @@
       </c>
     </row>
     <row r="47" spans="1:25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -24096,7 +24070,7 @@
       </c>
     </row>
     <row r="48" spans="1:25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -24155,7 +24129,7 @@
       </c>
     </row>
     <row r="49" spans="1:25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -24214,7 +24188,7 @@
       </c>
     </row>
     <row r="50" spans="1:25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -24264,7 +24238,7 @@
       </c>
     </row>
     <row r="51" spans="1:25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -24323,7 +24297,7 @@
       </c>
     </row>
     <row r="52" spans="1:25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -24352,7 +24326,7 @@
       </c>
     </row>
     <row r="53" spans="1:25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -24421,84 +24395,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>51</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>52</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>62</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>63</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>73</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>74</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>84</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -24566,7 +24540,7 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -24634,7 +24608,7 @@
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -24702,7 +24676,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -24770,7 +24744,7 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -24847,7 +24821,7 @@
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -24924,7 +24898,7 @@
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -25001,7 +24975,7 @@
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -25069,7 +25043,7 @@
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -25146,7 +25120,7 @@
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -25223,7 +25197,7 @@
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -25300,7 +25274,7 @@
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -25377,7 +25351,7 @@
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -25454,7 +25428,7 @@
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -25522,7 +25496,7 @@
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -25599,7 +25573,7 @@
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -25676,7 +25650,7 @@
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -25753,7 +25727,7 @@
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -25830,7 +25804,7 @@
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -25907,7 +25881,7 @@
       </c>
     </row>
     <row r="21" spans="1:25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -25984,7 +25958,7 @@
       </c>
     </row>
     <row r="22" spans="1:25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -26061,7 +26035,7 @@
       </c>
     </row>
     <row r="23" spans="1:25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -26138,7 +26112,7 @@
       </c>
     </row>
     <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -26215,7 +26189,7 @@
       </c>
     </row>
     <row r="25" spans="1:25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -26292,7 +26266,7 @@
       </c>
     </row>
     <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -26369,7 +26343,7 @@
       </c>
     </row>
     <row r="27" spans="1:25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -26446,7 +26420,7 @@
       </c>
     </row>
     <row r="28" spans="1:25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -26514,7 +26488,7 @@
       </c>
     </row>
     <row r="29" spans="1:25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -26591,7 +26565,7 @@
       </c>
     </row>
     <row r="30" spans="1:25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -26668,7 +26642,7 @@
       </c>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -26745,7 +26719,7 @@
       </c>
     </row>
     <row r="32" spans="1:25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -26822,7 +26796,7 @@
       </c>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -26899,7 +26873,7 @@
       </c>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -26976,7 +26950,7 @@
       </c>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -27053,7 +27027,7 @@
       </c>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -27130,7 +27104,7 @@
       </c>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -27207,7 +27181,7 @@
       </c>
     </row>
     <row r="38" spans="1:25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -27284,7 +27258,7 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -27361,7 +27335,7 @@
       </c>
     </row>
     <row r="40" spans="1:25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -27432,7 +27406,7 @@
       </c>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -27509,7 +27483,7 @@
       </c>
     </row>
     <row r="42" spans="1:25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -27586,7 +27560,7 @@
       </c>
     </row>
     <row r="43" spans="1:25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -27663,7 +27637,7 @@
       </c>
     </row>
     <row r="44" spans="1:25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -27740,7 +27714,7 @@
       </c>
     </row>
     <row r="45" spans="1:25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -27808,7 +27782,7 @@
       </c>
     </row>
     <row r="46" spans="1:25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -27885,7 +27859,7 @@
       </c>
     </row>
     <row r="47" spans="1:25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -27953,7 +27927,7 @@
       </c>
     </row>
     <row r="48" spans="1:25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -28030,7 +28004,7 @@
       </c>
     </row>
     <row r="49" spans="1:25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -28107,7 +28081,7 @@
       </c>
     </row>
     <row r="50" spans="1:25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -28175,7 +28149,7 @@
       </c>
     </row>
     <row r="51" spans="1:25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -28252,7 +28226,7 @@
       </c>
     </row>
     <row r="52" spans="1:25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -28329,7 +28303,7 @@
       </c>
     </row>
     <row r="53" spans="1:25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -28416,84 +28390,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>53</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>54</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>64</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>65</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>75</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>76</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>86</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -28561,7 +28535,7 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -28629,7 +28603,7 @@
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -28697,7 +28671,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -28765,7 +28739,7 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -28842,7 +28816,7 @@
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -28919,7 +28893,7 @@
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -28996,7 +28970,7 @@
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -29064,7 +29038,7 @@
       </c>
     </row>
     <row r="10" spans="1:25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -29141,7 +29115,7 @@
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -29218,7 +29192,7 @@
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -29295,7 +29269,7 @@
       </c>
     </row>
     <row r="13" spans="1:25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -29372,7 +29346,7 @@
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -29449,7 +29423,7 @@
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -29517,7 +29491,7 @@
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -29594,7 +29568,7 @@
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -29671,7 +29645,7 @@
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -29748,7 +29722,7 @@
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -29825,7 +29799,7 @@
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -29902,7 +29876,7 @@
       </c>
     </row>
     <row r="21" spans="1:25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -29979,7 +29953,7 @@
       </c>
     </row>
     <row r="22" spans="1:25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -30056,7 +30030,7 @@
       </c>
     </row>
     <row r="23" spans="1:25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -30133,7 +30107,7 @@
       </c>
     </row>
     <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -30210,7 +30184,7 @@
       </c>
     </row>
     <row r="25" spans="1:25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -30287,7 +30261,7 @@
       </c>
     </row>
     <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -30364,7 +30338,7 @@
       </c>
     </row>
     <row r="27" spans="1:25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -30441,7 +30415,7 @@
       </c>
     </row>
     <row r="28" spans="1:25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -30509,7 +30483,7 @@
       </c>
     </row>
     <row r="29" spans="1:25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -30586,7 +30560,7 @@
       </c>
     </row>
     <row r="30" spans="1:25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -30663,7 +30637,7 @@
       </c>
     </row>
     <row r="31" spans="1:25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -30740,7 +30714,7 @@
       </c>
     </row>
     <row r="32" spans="1:25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -30811,7 +30785,7 @@
       </c>
     </row>
     <row r="33" spans="1:25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -30888,7 +30862,7 @@
       </c>
     </row>
     <row r="34" spans="1:25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -30965,7 +30939,7 @@
       </c>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -31042,7 +31016,7 @@
       </c>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -31119,7 +31093,7 @@
       </c>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -31196,7 +31170,7 @@
       </c>
     </row>
     <row r="38" spans="1:25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -31273,7 +31247,7 @@
       </c>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -31344,7 +31318,7 @@
       </c>
     </row>
     <row r="40" spans="1:25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -31421,7 +31395,7 @@
       </c>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -31498,7 +31472,7 @@
       </c>
     </row>
     <row r="42" spans="1:25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -31575,7 +31549,7 @@
       </c>
     </row>
     <row r="43" spans="1:25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -31652,7 +31626,7 @@
       </c>
     </row>
     <row r="44" spans="1:25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -31729,7 +31703,7 @@
       </c>
     </row>
     <row r="45" spans="1:25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -31797,7 +31771,7 @@
       </c>
     </row>
     <row r="46" spans="1:25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -31874,7 +31848,7 @@
       </c>
     </row>
     <row r="47" spans="1:25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -31942,7 +31916,7 @@
       </c>
     </row>
     <row r="48" spans="1:25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -32019,7 +31993,7 @@
       </c>
     </row>
     <row r="49" spans="1:25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -32096,7 +32070,7 @@
       </c>
     </row>
     <row r="50" spans="1:25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -32164,7 +32138,7 @@
       </c>
     </row>
     <row r="51" spans="1:25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -32241,7 +32215,7 @@
       </c>
     </row>
     <row r="52" spans="1:25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -32318,7 +32292,7 @@
       </c>
     </row>
     <row r="53" spans="1:25">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
